--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CD45B7-E765-42B8-8427-14E7B73D7C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F099FDE8-DADB-45B0-801F-9FD6CD091D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1681">
   <si>
     <t>Walmart</t>
   </si>
@@ -5509,10 +5509,6 @@
   </si>
   <si>
     <t>jyhjrzcgyjzbd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易性金融资产-公允价变动</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -12082,7 +12078,7 @@
         <v>1658</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>1478</v>
@@ -12094,7 +12090,7 @@
         <v>11010001</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.2">
@@ -12105,7 +12101,7 @@
         <v>1658</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>1478</v>
@@ -12117,7 +12113,7 @@
         <v>1131</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.2">
@@ -12128,7 +12124,7 @@
         <v>1658</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>1478</v>
@@ -12140,7 +12136,7 @@
         <v>6111</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.2">
@@ -12151,7 +12147,7 @@
         <v>1658</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>1478</v>
@@ -12163,7 +12159,7 @@
         <v>1002</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.2">
@@ -12174,7 +12170,7 @@
         <v>1658</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>1478</v>
@@ -12186,7 +12182,7 @@
         <v>1101</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.2">
@@ -12197,7 +12193,7 @@
         <v>1658</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>1478</v>
@@ -12209,7 +12205,7 @@
         <v>1131</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.2">
@@ -12220,7 +12216,7 @@
         <v>1658</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>1478</v>
@@ -12232,7 +12228,7 @@
         <v>11010002</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.2">
@@ -12243,7 +12239,7 @@
         <v>1658</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>1478</v>
@@ -12255,7 +12251,7 @@
         <v>6101</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.2">
@@ -12266,7 +12262,7 @@
         <v>1658</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>1478</v>
@@ -12278,7 +12274,7 @@
         <v>1002</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.2">
@@ -12289,19 +12285,19 @@
         <v>1658</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1478</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H30" s="4">
         <v>6101</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.2">
@@ -12312,19 +12308,19 @@
         <v>1658</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>1478</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H31" s="4">
         <v>11010001</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.2">
@@ -12335,19 +12331,19 @@
         <v>1658</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>1478</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H32" s="13">
         <v>11010002</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.2">
@@ -12358,19 +12354,19 @@
         <v>1658</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>1478</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H33" s="13">
         <v>6111</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
   </sheetData>
@@ -13658,7 +13654,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>36462.19116173371</v>
+        <v>41816.910479381186</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -13683,7 +13679,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>40650.478653943996</v>
+        <v>42854.796229968677</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -13708,7 +13704,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43494.665566704687</v>
+        <v>40446.824715051138</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -13733,7 +13729,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39598.068841238033</v>
+        <v>38483.296644614806</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -13758,7 +13754,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42988.394199326794</v>
+        <v>44491.631509250597</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -13783,7 +13779,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41076.30354421425</v>
+        <v>41949.053834395614</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -13808,7 +13804,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38961.380645177465</v>
+        <v>40184.376413753358</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -13833,7 +13829,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38733.65172630961</v>
+        <v>44515.603986044829</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -13858,7 +13854,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39504.777361978646</v>
+        <v>40347.014144695684</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -13883,7 +13879,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38246.094397176035</v>
+        <v>44435.606146505837</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -13908,7 +13904,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42094.707302000978</v>
+        <v>36589.831975981113</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -13933,7 +13929,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42706.62661744724</v>
+        <v>40871.640164229153</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -13958,7 +13954,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40049.8609008192</v>
+        <v>39862.965190828778</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -13983,7 +13979,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42976.133546565237</v>
+        <v>40095.587748925449</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -14008,7 +14004,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42776.216018835978</v>
+        <v>39755.820185622586</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -14033,7 +14029,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41541.743368719035</v>
+        <v>38193.737130713176</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -14058,7 +14054,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41657.737736326329</v>
+        <v>39477.186906505514</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -14083,7 +14079,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38012.384504336296</v>
+        <v>37815.147281724014</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -14108,7 +14104,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40998.856069032008</v>
+        <v>39600.314115282883</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -14133,7 +14129,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40189.717382475726</v>
+        <v>35984.882328682565</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -14158,7 +14154,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42632.070420160802</v>
+        <v>40619.370693400975</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -14183,7 +14179,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37628.288791772997</v>
+        <v>42994.44256820577</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -14208,7 +14204,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42475.46577952207</v>
+        <v>41449.181934317341</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -14233,7 +14229,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42866.841908656912</v>
+        <v>40717.911392591952</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -14258,7 +14254,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40228.647728721829</v>
+        <v>41760.779290306484</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -14283,7 +14279,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38655.359405622265</v>
+        <v>42663.311027247131</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -14308,7 +14304,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35478.828190211119</v>
+        <v>40401.48584528362</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -14333,7 +14329,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44885.771615944483</v>
+        <v>44443.551766008582</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -14358,7 +14354,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41559.292424645631</v>
+        <v>38849.380234274489</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -14383,7 +14379,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44969.778601636273</v>
+        <v>39485.043712631414</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -16032,7 +16028,7 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>1662</v>
+        <v>1677</v>
       </c>
       <c r="E13" t="s">
         <v>1661</v>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F099FDE8-DADB-45B0-801F-9FD6CD091D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15C2EE-2779-48E4-A7D9-D2B16E0897EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -12179,7 +12179,7 @@
         <v>1479</v>
       </c>
       <c r="H25" s="4">
-        <v>1101</v>
+        <v>1002</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1662</v>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>41816.910479381186</v>
+        <v>41086.298512739813</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -13679,7 +13679,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>42854.796229968677</v>
+        <v>36311.143891502274</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40446.824715051138</v>
+        <v>36030.32095808757</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38483.296644614806</v>
+        <v>35823.978477838449</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44491.631509250597</v>
+        <v>39941.822488793776</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41949.053834395614</v>
+        <v>44877.458957798721</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40184.376413753358</v>
+        <v>37022.670169279605</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44515.603986044829</v>
+        <v>43492.13689093796</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40347.014144695684</v>
+        <v>35403.986652448104</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44435.606146505837</v>
+        <v>42380.519684610452</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -13904,7 +13904,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36589.831975981113</v>
+        <v>37880.344942531068</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -13929,7 +13929,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40871.640164229153</v>
+        <v>39517.568113506815</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -13954,7 +13954,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39862.965190828778</v>
+        <v>39385.206232741155</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40095.587748925449</v>
+        <v>42155.873668374923</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39755.820185622586</v>
+        <v>44553.774232714561</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38193.737130713176</v>
+        <v>37842.143973586899</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39477.186906505514</v>
+        <v>39439.262099355452</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37815.147281724014</v>
+        <v>44384.749183341999</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39600.314115282883</v>
+        <v>36102.301563439258</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -14129,7 +14129,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35984.882328682565</v>
+        <v>38140.752910981457</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -14154,7 +14154,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40619.370693400975</v>
+        <v>37836.467535914395</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -14179,7 +14179,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42994.44256820577</v>
+        <v>44260.695678379467</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41449.181934317341</v>
+        <v>38332.459146021974</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -14229,7 +14229,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40717.911392591952</v>
+        <v>35910.579536969199</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -14254,7 +14254,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41760.779290306484</v>
+        <v>44593.059199929303</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42663.311027247131</v>
+        <v>35482.812724656935</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40401.48584528362</v>
+        <v>38683.152075218306</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44443.551766008582</v>
+        <v>39060.24283354517</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38849.380234274489</v>
+        <v>36219.892019753403</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39485.043712631414</v>
+        <v>36062.678588222567</v>
       </c>
       <c r="F32">
         <v>123456</v>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D15C2EE-2779-48E4-A7D9-D2B16E0897EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F23793-2B98-4C6C-A9C5-F6D98CBFBA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="1681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="1702">
   <si>
     <t>Walmart</t>
   </si>
@@ -5585,6 +5585,84 @@
   </si>
   <si>
     <t>1000#策略/交易性金融资产-出售股票/长头/平衡/银行存款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有至到期投资-初始确认</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>持有至到期投资-成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有至到期投资-利息调整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/借/持有至到期投资-成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/贷/银行存款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/平衡/持有至到期投资-利息调整</t>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/平衡/持有至到期投资-利息调整</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POLICY1000</t>
+  </si>
+  <si>
+    <t>LONG</t>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/借/应收利息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/贷/投资收益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/借/银行存款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-初始确认/长头/平衡/投资收益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有至到期投资-后续计量-资产负债表日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有至到期投资-后续计量-银行收款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>持有至到期投资-到期处置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-到期处置/长头/借/银行存款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000#策略/持有至到期投资-到期处置/长头/借/持有至到期投资-成本</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5733,7 +5811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5748,6 +5826,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11621,12 +11700,12 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BAB75F4-CF88-4683-9DC4-6FEC4CE23155}">
-  <dimension ref="C2:I33"/>
+  <dimension ref="C2:I43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="3.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
@@ -12367,6 +12446,236 @@
       </c>
       <c r="I33" s="4" t="s">
         <v>1679</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C34" s="5">
+        <v>32</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H34" s="5">
+        <v>15210001</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C35" s="5">
+        <v>33</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H35" s="5">
+        <v>15210002</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C36" s="5">
+        <v>34</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H36" s="5">
+        <v>1002</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C37" s="4">
+        <v>35</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H37" s="4">
+        <v>15210001</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C38" s="4">
+        <v>36</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="H38" s="4">
+        <v>15210002</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C39" s="4">
+        <v>37</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="H39" s="4">
+        <v>6111</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C40" s="5">
+        <v>38</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H40" s="5">
+        <v>1002</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C41" s="5">
+        <v>39</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>1698</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>1480</v>
+      </c>
+      <c r="H41" s="5">
+        <v>1132</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C42" s="14">
+        <v>40</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H42" s="4">
+        <v>1002</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C43" s="14">
+        <v>41</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H43" s="4">
+        <v>1002</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>1701</v>
       </c>
     </row>
   </sheetData>
@@ -13654,7 +13963,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>41086.298512739813</v>
+        <v>40926.496965423699</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -13679,7 +13988,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>36311.143891502274</v>
+        <v>40520.280178656205</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -13704,7 +14013,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36030.32095808757</v>
+        <v>38107.782219386296</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -13729,7 +14038,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35823.978477838449</v>
+        <v>40459.557431692112</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -13754,7 +14063,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39941.822488793776</v>
+        <v>44653.680435386668</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -13779,7 +14088,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44877.458957798721</v>
+        <v>41844.316229127668</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -13804,7 +14113,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37022.670169279605</v>
+        <v>39185.304680449022</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -13829,7 +14138,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43492.13689093796</v>
+        <v>41974.535348533238</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -13854,7 +14163,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35403.986652448104</v>
+        <v>45104.668034847869</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -13879,7 +14188,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42380.519684610452</v>
+        <v>38644.253369335856</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -13904,7 +14213,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37880.344942531068</v>
+        <v>44898.359436510029</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -13929,7 +14238,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39517.568113506815</v>
+        <v>44991.569935888845</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -13954,7 +14263,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39385.206232741155</v>
+        <v>42336.543804867448</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -13979,7 +14288,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42155.873668374923</v>
+        <v>38677.342438012965</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -14004,7 +14313,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44553.774232714561</v>
+        <v>38925.508798756033</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -14029,7 +14338,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37842.143973586899</v>
+        <v>41342.154797522737</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -14054,7 +14363,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39439.262099355452</v>
+        <v>44292.107325674115</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -14079,7 +14388,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44384.749183341999</v>
+        <v>36102.61652407088</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -14104,7 +14413,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36102.301563439258</v>
+        <v>41324.969808373193</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -14129,7 +14438,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38140.752910981457</v>
+        <v>39479.904782327823</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -14154,7 +14463,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37836.467535914395</v>
+        <v>36376.868241241013</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -14179,7 +14488,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44260.695678379467</v>
+        <v>42189.556548641805</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -14204,7 +14513,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38332.459146021974</v>
+        <v>38928.897679568647</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -14229,7 +14538,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35910.579536969199</v>
+        <v>43195.560745696501</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -14254,7 +14563,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44593.059199929303</v>
+        <v>38256.163723931735</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -14279,7 +14588,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>35482.812724656935</v>
+        <v>38486.296590376187</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -14304,7 +14613,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38683.152075218306</v>
+        <v>39672.506993358853</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -14329,7 +14638,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39060.24283354517</v>
+        <v>43054.10866466639</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -14354,7 +14663,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36219.892019753403</v>
+        <v>39234.389292513188</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -14379,7 +14688,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36062.678588222567</v>
+        <v>42295.59702522571</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -15792,7 +16101,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A2A9196-0700-4745-A3DA-91F6FE5687B3}">
-  <dimension ref="C2:H165"/>
+  <dimension ref="C2:H167"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
@@ -16748,16 +17057,16 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>1172</v>
+        <v>1684</v>
       </c>
       <c r="E49" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F49" t="s">
         <v>1081</v>
       </c>
       <c r="G49">
-        <v>1522</v>
+        <v>15210001</v>
       </c>
       <c r="H49" t="s">
         <v>1416</v>
@@ -16768,16 +17077,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>1174</v>
+        <v>1685</v>
       </c>
       <c r="E50" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="F50" t="s">
         <v>1081</v>
       </c>
       <c r="G50">
-        <v>1523</v>
+        <v>15210002</v>
       </c>
       <c r="H50" t="s">
         <v>1416</v>
@@ -16788,16 +17097,16 @@
         <v>49</v>
       </c>
       <c r="D51" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="E51" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="F51" t="s">
         <v>1081</v>
       </c>
       <c r="G51">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="H51" t="s">
         <v>1416</v>
@@ -16808,16 +17117,16 @@
         <v>50</v>
       </c>
       <c r="D52" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="E52" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="F52" t="s">
         <v>1081</v>
       </c>
       <c r="G52">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="H52" t="s">
         <v>1416</v>
@@ -16828,16 +17137,16 @@
         <v>51</v>
       </c>
       <c r="D53" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E53" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="F53" t="s">
         <v>1081</v>
       </c>
       <c r="G53">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="H53" t="s">
         <v>1416</v>
@@ -16848,16 +17157,16 @@
         <v>52</v>
       </c>
       <c r="D54" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="E54" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="F54" t="s">
         <v>1081</v>
       </c>
       <c r="G54">
-        <v>1531</v>
+        <v>1525</v>
       </c>
       <c r="H54" t="s">
         <v>1416</v>
@@ -16868,16 +17177,16 @@
         <v>53</v>
       </c>
       <c r="D55" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="E55" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="F55" t="s">
         <v>1081</v>
       </c>
       <c r="G55">
-        <v>1541</v>
+        <v>1526</v>
       </c>
       <c r="H55" t="s">
         <v>1416</v>
@@ -16888,19 +17197,19 @@
         <v>54</v>
       </c>
       <c r="D56" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="E56" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="F56" t="s">
         <v>1081</v>
       </c>
       <c r="G56">
-        <v>1551</v>
+        <v>1531</v>
       </c>
       <c r="H56" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.2">
@@ -16908,16 +17217,16 @@
         <v>55</v>
       </c>
       <c r="D57" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="E57" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="F57" t="s">
         <v>1081</v>
       </c>
       <c r="G57">
-        <v>1601</v>
+        <v>1541</v>
       </c>
       <c r="H57" t="s">
         <v>1416</v>
@@ -16928,19 +17237,19 @@
         <v>56</v>
       </c>
       <c r="D58" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="E58" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="F58" t="s">
         <v>1081</v>
       </c>
       <c r="G58">
-        <v>1602</v>
+        <v>1551</v>
       </c>
       <c r="H58" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.2">
@@ -16948,16 +17257,16 @@
         <v>57</v>
       </c>
       <c r="D59" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="E59" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="F59" t="s">
         <v>1081</v>
       </c>
       <c r="G59">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="H59" t="s">
         <v>1416</v>
@@ -16968,16 +17277,16 @@
         <v>58</v>
       </c>
       <c r="D60" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="E60" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="F60" t="s">
         <v>1081</v>
       </c>
       <c r="G60">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="H60" t="s">
         <v>1416</v>
@@ -16988,16 +17297,16 @@
         <v>59</v>
       </c>
       <c r="D61" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="E61" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="F61" t="s">
         <v>1081</v>
       </c>
       <c r="G61">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="H61" t="s">
         <v>1416</v>
@@ -17008,16 +17317,16 @@
         <v>60</v>
       </c>
       <c r="D62" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="E62" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="F62" t="s">
         <v>1081</v>
       </c>
       <c r="G62">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="H62" t="s">
         <v>1416</v>
@@ -17028,19 +17337,19 @@
         <v>61</v>
       </c>
       <c r="D63" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="E63" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="F63" t="s">
         <v>1081</v>
       </c>
       <c r="G63">
-        <v>1611</v>
+        <v>1605</v>
       </c>
       <c r="H63" t="s">
-        <v>1202</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.2">
@@ -17048,19 +17357,19 @@
         <v>62</v>
       </c>
       <c r="D64" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="E64" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="F64" t="s">
         <v>1081</v>
       </c>
       <c r="G64">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="H64" t="s">
-        <v>1202</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="65" spans="3:8" x14ac:dyDescent="0.2">
@@ -17068,19 +17377,19 @@
         <v>63</v>
       </c>
       <c r="D65" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="E65" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="F65" t="s">
         <v>1081</v>
       </c>
       <c r="G65">
-        <v>1621</v>
+        <v>1611</v>
       </c>
       <c r="H65" t="s">
-        <v>1156</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="66" spans="3:8" x14ac:dyDescent="0.2">
@@ -17088,19 +17397,19 @@
         <v>64</v>
       </c>
       <c r="D66" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E66" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="F66" t="s">
         <v>1081</v>
       </c>
       <c r="G66">
-        <v>1622</v>
+        <v>1612</v>
       </c>
       <c r="H66" t="s">
-        <v>1156</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="67" spans="3:8" x14ac:dyDescent="0.2">
@@ -17108,16 +17417,16 @@
         <v>65</v>
       </c>
       <c r="D67" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="E67" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="F67" t="s">
         <v>1081</v>
       </c>
       <c r="G67">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="H67" t="s">
         <v>1156</v>
@@ -17128,19 +17437,19 @@
         <v>66</v>
       </c>
       <c r="D68" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="E68" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="F68" t="s">
         <v>1081</v>
       </c>
       <c r="G68">
-        <v>1631</v>
+        <v>1622</v>
       </c>
       <c r="H68" t="s">
-        <v>1213</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.2">
@@ -17148,19 +17457,19 @@
         <v>67</v>
       </c>
       <c r="D69" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="E69" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="F69" t="s">
         <v>1081</v>
       </c>
       <c r="G69">
-        <v>1632</v>
+        <v>1623</v>
       </c>
       <c r="H69" t="s">
-        <v>1213</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.2">
@@ -17168,19 +17477,19 @@
         <v>68</v>
       </c>
       <c r="D70" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="E70" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F70" t="s">
         <v>1081</v>
       </c>
       <c r="G70">
-        <v>1701</v>
+        <v>1631</v>
       </c>
       <c r="H70" t="s">
-        <v>1416</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.2">
@@ -17188,19 +17497,19 @@
         <v>69</v>
       </c>
       <c r="D71" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="E71" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="F71" t="s">
         <v>1081</v>
       </c>
       <c r="G71">
-        <v>1702</v>
+        <v>1632</v>
       </c>
       <c r="H71" t="s">
-        <v>1416</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.2">
@@ -17208,16 +17517,16 @@
         <v>70</v>
       </c>
       <c r="D72" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E72" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="F72" t="s">
         <v>1081</v>
       </c>
       <c r="G72">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="H72" t="s">
         <v>1416</v>
@@ -17228,16 +17537,16 @@
         <v>71</v>
       </c>
       <c r="D73" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="E73" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="F73" t="s">
         <v>1081</v>
       </c>
       <c r="G73">
-        <v>1711</v>
+        <v>1702</v>
       </c>
       <c r="H73" t="s">
         <v>1416</v>
@@ -17248,16 +17557,16 @@
         <v>72</v>
       </c>
       <c r="D74" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E74" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="F74" t="s">
         <v>1081</v>
       </c>
       <c r="G74">
-        <v>1801</v>
+        <v>1703</v>
       </c>
       <c r="H74" t="s">
         <v>1416</v>
@@ -17268,16 +17577,16 @@
         <v>73</v>
       </c>
       <c r="D75" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E75" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="F75" t="s">
         <v>1081</v>
       </c>
       <c r="G75">
-        <v>1811</v>
+        <v>1711</v>
       </c>
       <c r="H75" t="s">
         <v>1416</v>
@@ -17288,16 +17597,16 @@
         <v>74</v>
       </c>
       <c r="D76" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="E76" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="F76" t="s">
         <v>1081</v>
       </c>
       <c r="G76">
-        <v>1901</v>
+        <v>1801</v>
       </c>
       <c r="H76" t="s">
         <v>1416</v>
@@ -17308,16 +17617,16 @@
         <v>75</v>
       </c>
       <c r="D77" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E77" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="F77" t="s">
-        <v>1232</v>
+        <v>1081</v>
       </c>
       <c r="G77">
-        <v>2001</v>
+        <v>1811</v>
       </c>
       <c r="H77" t="s">
         <v>1416</v>
@@ -17328,19 +17637,19 @@
         <v>76</v>
       </c>
       <c r="D78" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="E78" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="F78" t="s">
-        <v>1232</v>
+        <v>1081</v>
       </c>
       <c r="G78">
-        <v>2002</v>
+        <v>1901</v>
       </c>
       <c r="H78" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.2">
@@ -17348,19 +17657,19 @@
         <v>77</v>
       </c>
       <c r="D79" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="E79" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F79" t="s">
         <v>1232</v>
       </c>
       <c r="G79">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="H79" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.2">
@@ -17368,19 +17677,19 @@
         <v>78</v>
       </c>
       <c r="D80" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="E80" t="s">
-        <v>1415</v>
+        <v>1234</v>
       </c>
       <c r="F80" t="s">
         <v>1232</v>
       </c>
       <c r="G80">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H80" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.2">
@@ -17388,19 +17697,19 @@
         <v>79</v>
       </c>
       <c r="D81" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="E81" t="s">
-        <v>1239</v>
+        <v>1236</v>
       </c>
       <c r="F81" t="s">
         <v>1232</v>
       </c>
       <c r="G81">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="H81" t="s">
-        <v>1084</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.2">
@@ -17408,16 +17717,16 @@
         <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="E82" t="s">
-        <v>1241</v>
+        <v>1415</v>
       </c>
       <c r="F82" t="s">
         <v>1232</v>
       </c>
       <c r="G82">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="H82" t="s">
         <v>1084</v>
@@ -17428,16 +17737,16 @@
         <v>81</v>
       </c>
       <c r="D83" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="E83" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="F83" t="s">
         <v>1232</v>
       </c>
       <c r="G83">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="H83" t="s">
         <v>1084</v>
@@ -17448,19 +17757,19 @@
         <v>82</v>
       </c>
       <c r="D84" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="E84" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="F84" t="s">
         <v>1232</v>
       </c>
       <c r="G84">
-        <v>2101</v>
+        <v>2012</v>
       </c>
       <c r="H84" t="s">
-        <v>1416</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="85" spans="3:8" x14ac:dyDescent="0.2">
@@ -17468,19 +17777,19 @@
         <v>83</v>
       </c>
       <c r="D85" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="E85" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="F85" t="s">
         <v>1232</v>
       </c>
       <c r="G85">
-        <v>2111</v>
+        <v>2021</v>
       </c>
       <c r="H85" t="s">
-        <v>1094</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="86" spans="3:8" x14ac:dyDescent="0.2">
@@ -17488,16 +17797,16 @@
         <v>84</v>
       </c>
       <c r="D86" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="E86" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="F86" t="s">
         <v>1232</v>
       </c>
       <c r="G86">
-        <v>2201</v>
+        <v>2101</v>
       </c>
       <c r="H86" t="s">
         <v>1416</v>
@@ -17508,19 +17817,19 @@
         <v>85</v>
       </c>
       <c r="D87" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E87" t="s">
-        <v>1105</v>
+        <v>1247</v>
       </c>
       <c r="F87" t="s">
         <v>1232</v>
       </c>
       <c r="G87">
-        <v>2202</v>
+        <v>2111</v>
       </c>
       <c r="H87" t="s">
-        <v>1416</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="88" spans="3:8" x14ac:dyDescent="0.2">
@@ -17528,16 +17837,16 @@
         <v>86</v>
       </c>
       <c r="D88" t="s">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="E88" t="s">
-        <v>1103</v>
+        <v>1249</v>
       </c>
       <c r="F88" t="s">
         <v>1232</v>
       </c>
       <c r="G88">
-        <v>2205</v>
+        <v>2201</v>
       </c>
       <c r="H88" t="s">
         <v>1416</v>
@@ -17548,16 +17857,16 @@
         <v>87</v>
       </c>
       <c r="D89" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="E89" t="s">
-        <v>1253</v>
+        <v>1105</v>
       </c>
       <c r="F89" t="s">
         <v>1232</v>
       </c>
       <c r="G89">
-        <v>2211</v>
+        <v>2202</v>
       </c>
       <c r="H89" t="s">
         <v>1416</v>
@@ -17568,16 +17877,16 @@
         <v>88</v>
       </c>
       <c r="D90" t="s">
-        <v>1254</v>
+        <v>1251</v>
       </c>
       <c r="E90" t="s">
-        <v>1255</v>
+        <v>1103</v>
       </c>
       <c r="F90" t="s">
         <v>1232</v>
       </c>
       <c r="G90">
-        <v>2221</v>
+        <v>2205</v>
       </c>
       <c r="H90" t="s">
         <v>1416</v>
@@ -17588,16 +17897,16 @@
         <v>89</v>
       </c>
       <c r="D91" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="E91" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="F91" t="s">
         <v>1232</v>
       </c>
       <c r="G91">
-        <v>2231</v>
+        <v>2211</v>
       </c>
       <c r="H91" t="s">
         <v>1416</v>
@@ -17608,16 +17917,16 @@
         <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="E92" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="F92" t="s">
         <v>1232</v>
       </c>
       <c r="G92">
-        <v>2232</v>
+        <v>2221</v>
       </c>
       <c r="H92" t="s">
         <v>1416</v>
@@ -17628,16 +17937,16 @@
         <v>91</v>
       </c>
       <c r="D93" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="E93" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="F93" t="s">
         <v>1232</v>
       </c>
       <c r="G93">
-        <v>2241</v>
+        <v>2231</v>
       </c>
       <c r="H93" t="s">
         <v>1416</v>
@@ -17648,19 +17957,19 @@
         <v>92</v>
       </c>
       <c r="D94" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E94" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="F94" t="s">
         <v>1232</v>
       </c>
       <c r="G94">
-        <v>2251</v>
+        <v>2232</v>
       </c>
       <c r="H94" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="95" spans="3:8" x14ac:dyDescent="0.2">
@@ -17668,19 +17977,19 @@
         <v>93</v>
       </c>
       <c r="D95" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="E95" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="F95" t="s">
         <v>1232</v>
       </c>
       <c r="G95">
-        <v>2261</v>
+        <v>2241</v>
       </c>
       <c r="H95" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="96" spans="3:8" x14ac:dyDescent="0.2">
@@ -17688,19 +17997,19 @@
         <v>94</v>
       </c>
       <c r="D96" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="E96" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="F96" t="s">
         <v>1232</v>
       </c>
       <c r="G96">
-        <v>2311</v>
+        <v>2251</v>
       </c>
       <c r="H96" t="s">
-        <v>1091</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="97" spans="3:8" x14ac:dyDescent="0.2">
@@ -17708,19 +18017,19 @@
         <v>95</v>
       </c>
       <c r="D97" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="E97" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="F97" t="s">
         <v>1232</v>
       </c>
       <c r="G97">
-        <v>2312</v>
+        <v>2261</v>
       </c>
       <c r="H97" t="s">
-        <v>1270</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="98" spans="3:8" x14ac:dyDescent="0.2">
@@ -17728,19 +18037,19 @@
         <v>96</v>
       </c>
       <c r="D98" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="E98" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="F98" t="s">
         <v>1232</v>
       </c>
       <c r="G98">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="H98" t="s">
-        <v>1270</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="99" spans="3:8" x14ac:dyDescent="0.2">
@@ -17748,19 +18057,19 @@
         <v>97</v>
       </c>
       <c r="D99" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="E99" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="F99" t="s">
         <v>1232</v>
       </c>
       <c r="G99">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="H99" t="s">
-        <v>1416</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="100" spans="3:8" x14ac:dyDescent="0.2">
@@ -17768,19 +18077,19 @@
         <v>98</v>
       </c>
       <c r="D100" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="E100" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F100" t="s">
         <v>1232</v>
       </c>
       <c r="G100">
-        <v>2401</v>
+        <v>2313</v>
       </c>
       <c r="H100" t="s">
-        <v>1416</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="101" spans="3:8" x14ac:dyDescent="0.2">
@@ -17788,16 +18097,16 @@
         <v>99</v>
       </c>
       <c r="D101" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="E101" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="F101" t="s">
         <v>1232</v>
       </c>
       <c r="G101">
-        <v>2411</v>
+        <v>2314</v>
       </c>
       <c r="H101" t="s">
         <v>1416</v>
@@ -17808,16 +18117,16 @@
         <v>100</v>
       </c>
       <c r="D102" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="E102" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="F102" t="s">
         <v>1232</v>
       </c>
       <c r="G102">
-        <v>2501</v>
+        <v>2401</v>
       </c>
       <c r="H102" t="s">
         <v>1416</v>
@@ -17828,16 +18137,16 @@
         <v>101</v>
       </c>
       <c r="D103" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="E103" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="F103" t="s">
         <v>1232</v>
       </c>
       <c r="G103">
-        <v>2601</v>
+        <v>2411</v>
       </c>
       <c r="H103" t="s">
         <v>1416</v>
@@ -17848,16 +18157,16 @@
         <v>102</v>
       </c>
       <c r="D104" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="E104" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="F104" t="s">
         <v>1232</v>
       </c>
       <c r="G104">
-        <v>2602</v>
+        <v>2501</v>
       </c>
       <c r="H104" t="s">
         <v>1416</v>
@@ -17868,19 +18177,19 @@
         <v>103</v>
       </c>
       <c r="D105" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="E105" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="F105" t="s">
         <v>1232</v>
       </c>
       <c r="G105">
-        <v>2701</v>
+        <v>2601</v>
       </c>
       <c r="H105" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="106" spans="3:8" x14ac:dyDescent="0.2">
@@ -17888,19 +18197,19 @@
         <v>104</v>
       </c>
       <c r="D106" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="E106" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="F106" t="s">
         <v>1232</v>
       </c>
       <c r="G106">
-        <v>2702</v>
+        <v>2602</v>
       </c>
       <c r="H106" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="107" spans="3:8" x14ac:dyDescent="0.2">
@@ -17908,16 +18217,16 @@
         <v>105</v>
       </c>
       <c r="D107" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="E107" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="F107" t="s">
         <v>1232</v>
       </c>
       <c r="G107">
-        <v>2711</v>
+        <v>2701</v>
       </c>
       <c r="H107" t="s">
         <v>1112</v>
@@ -17928,16 +18237,16 @@
         <v>106</v>
       </c>
       <c r="D108" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="E108" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="F108" t="s">
         <v>1232</v>
       </c>
       <c r="G108">
-        <v>2721</v>
+        <v>2702</v>
       </c>
       <c r="H108" t="s">
         <v>1112</v>
@@ -17948,19 +18257,19 @@
         <v>107</v>
       </c>
       <c r="D109" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="E109" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="F109" t="s">
         <v>1232</v>
       </c>
       <c r="G109">
-        <v>2801</v>
+        <v>2711</v>
       </c>
       <c r="H109" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="110" spans="3:8" x14ac:dyDescent="0.2">
@@ -17968,19 +18277,19 @@
         <v>108</v>
       </c>
       <c r="D110" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="E110" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="F110" t="s">
         <v>1232</v>
       </c>
       <c r="G110">
-        <v>2802</v>
+        <v>2721</v>
       </c>
       <c r="H110" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="111" spans="3:8" x14ac:dyDescent="0.2">
@@ -17988,16 +18297,16 @@
         <v>109</v>
       </c>
       <c r="D111" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="E111" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="F111" t="s">
         <v>1232</v>
       </c>
       <c r="G111">
-        <v>2811</v>
+        <v>2801</v>
       </c>
       <c r="H111" t="s">
         <v>1416</v>
@@ -18008,16 +18317,16 @@
         <v>110</v>
       </c>
       <c r="D112" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="E112" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="F112" t="s">
         <v>1232</v>
       </c>
       <c r="G112">
-        <v>2901</v>
+        <v>2802</v>
       </c>
       <c r="H112" t="s">
         <v>1416</v>
@@ -18028,19 +18337,19 @@
         <v>111</v>
       </c>
       <c r="D113" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="E113" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="F113" t="s">
-        <v>1303</v>
+        <v>1232</v>
       </c>
       <c r="G113">
-        <v>3001</v>
+        <v>2811</v>
       </c>
       <c r="H113" t="s">
-        <v>1084</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="114" spans="3:8" x14ac:dyDescent="0.2">
@@ -18048,19 +18357,19 @@
         <v>112</v>
       </c>
       <c r="D114" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="E114" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="F114" t="s">
-        <v>1303</v>
+        <v>1232</v>
       </c>
       <c r="G114">
-        <v>3002</v>
+        <v>2901</v>
       </c>
       <c r="H114" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="115" spans="3:8" x14ac:dyDescent="0.2">
@@ -18068,19 +18377,19 @@
         <v>113</v>
       </c>
       <c r="D115" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="E115" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="F115" t="s">
         <v>1303</v>
       </c>
       <c r="G115">
-        <v>3101</v>
+        <v>3001</v>
       </c>
       <c r="H115" t="s">
-        <v>1416</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="116" spans="3:8" x14ac:dyDescent="0.2">
@@ -18088,19 +18397,19 @@
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E116" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="F116" t="s">
         <v>1303</v>
       </c>
       <c r="G116">
-        <v>3201</v>
+        <v>3002</v>
       </c>
       <c r="H116" t="s">
-        <v>1416</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="117" spans="3:8" x14ac:dyDescent="0.2">
@@ -18108,16 +18417,16 @@
         <v>115</v>
       </c>
       <c r="D117" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="E117" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="F117" t="s">
         <v>1303</v>
       </c>
       <c r="G117">
-        <v>3202</v>
+        <v>3101</v>
       </c>
       <c r="H117" t="s">
         <v>1416</v>
@@ -18128,16 +18437,16 @@
         <v>116</v>
       </c>
       <c r="D118" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="E118" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="F118" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="G118">
-        <v>4001</v>
+        <v>3201</v>
       </c>
       <c r="H118" t="s">
         <v>1416</v>
@@ -18148,16 +18457,16 @@
         <v>117</v>
       </c>
       <c r="D119" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="E119" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="F119" t="s">
-        <v>1314</v>
+        <v>1303</v>
       </c>
       <c r="G119">
-        <v>4002</v>
+        <v>3202</v>
       </c>
       <c r="H119" t="s">
         <v>1416</v>
@@ -18168,16 +18477,16 @@
         <v>118</v>
       </c>
       <c r="D120" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="E120" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F120" t="s">
         <v>1314</v>
       </c>
       <c r="G120">
-        <v>4101</v>
+        <v>4001</v>
       </c>
       <c r="H120" t="s">
         <v>1416</v>
@@ -18188,19 +18497,19 @@
         <v>119</v>
       </c>
       <c r="D121" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E121" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="F121" t="s">
         <v>1314</v>
       </c>
       <c r="G121">
-        <v>4102</v>
+        <v>4002</v>
       </c>
       <c r="H121" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="122" spans="3:8" x14ac:dyDescent="0.2">
@@ -18208,16 +18517,16 @@
         <v>120</v>
       </c>
       <c r="D122" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="E122" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="F122" t="s">
         <v>1314</v>
       </c>
       <c r="G122">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="H122" t="s">
         <v>1416</v>
@@ -18228,19 +18537,19 @@
         <v>121</v>
       </c>
       <c r="D123" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="E123" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="F123" t="s">
         <v>1314</v>
       </c>
       <c r="G123">
-        <v>4104</v>
+        <v>4102</v>
       </c>
       <c r="H123" t="s">
-        <v>1416</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="124" spans="3:8" x14ac:dyDescent="0.2">
@@ -18248,16 +18557,16 @@
         <v>122</v>
       </c>
       <c r="D124" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="E124" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="F124" t="s">
         <v>1314</v>
       </c>
       <c r="G124">
-        <v>4201</v>
+        <v>4103</v>
       </c>
       <c r="H124" t="s">
         <v>1416</v>
@@ -18268,16 +18577,16 @@
         <v>123</v>
       </c>
       <c r="D125" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="E125" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="F125" t="s">
-        <v>1329</v>
+        <v>1314</v>
       </c>
       <c r="G125">
-        <v>5001</v>
+        <v>4104</v>
       </c>
       <c r="H125" t="s">
         <v>1416</v>
@@ -18288,16 +18597,16 @@
         <v>124</v>
       </c>
       <c r="D126" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="E126" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="F126" t="s">
-        <v>1329</v>
+        <v>1314</v>
       </c>
       <c r="G126">
-        <v>5101</v>
+        <v>4201</v>
       </c>
       <c r="H126" t="s">
         <v>1416</v>
@@ -18308,16 +18617,16 @@
         <v>125</v>
       </c>
       <c r="D127" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="E127" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="F127" t="s">
         <v>1329</v>
       </c>
       <c r="G127">
-        <v>5201</v>
+        <v>5001</v>
       </c>
       <c r="H127" t="s">
         <v>1416</v>
@@ -18328,16 +18637,16 @@
         <v>126</v>
       </c>
       <c r="D128" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="E128" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="F128" t="s">
         <v>1329</v>
       </c>
       <c r="G128">
-        <v>5301</v>
+        <v>5101</v>
       </c>
       <c r="H128" t="s">
         <v>1416</v>
@@ -18348,19 +18657,19 @@
         <v>127</v>
       </c>
       <c r="D129" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="E129" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="F129" t="s">
         <v>1329</v>
       </c>
       <c r="G129">
-        <v>5401</v>
+        <v>5201</v>
       </c>
       <c r="H129" t="s">
-        <v>1159</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="130" spans="3:8" x14ac:dyDescent="0.2">
@@ -18368,19 +18677,19 @@
         <v>128</v>
       </c>
       <c r="D130" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="E130" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="F130" t="s">
         <v>1329</v>
       </c>
       <c r="G130">
-        <v>5402</v>
+        <v>5301</v>
       </c>
       <c r="H130" t="s">
-        <v>1159</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="131" spans="3:8" x14ac:dyDescent="0.2">
@@ -18388,16 +18697,16 @@
         <v>129</v>
       </c>
       <c r="D131" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="E131" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="F131" t="s">
         <v>1329</v>
       </c>
       <c r="G131">
-        <v>5403</v>
+        <v>5401</v>
       </c>
       <c r="H131" t="s">
         <v>1159</v>
@@ -18408,19 +18717,19 @@
         <v>130</v>
       </c>
       <c r="D132" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="E132" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="F132" t="s">
-        <v>1344</v>
+        <v>1329</v>
       </c>
       <c r="G132">
-        <v>6001</v>
+        <v>5402</v>
       </c>
       <c r="H132" t="s">
-        <v>1416</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="133" spans="3:8" x14ac:dyDescent="0.2">
@@ -18428,19 +18737,19 @@
         <v>131</v>
       </c>
       <c r="D133" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="E133" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="F133" t="s">
-        <v>1344</v>
+        <v>1329</v>
       </c>
       <c r="G133">
-        <v>6011</v>
+        <v>5403</v>
       </c>
       <c r="H133" t="s">
-        <v>1094</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="134" spans="3:8" x14ac:dyDescent="0.2">
@@ -18448,19 +18757,19 @@
         <v>132</v>
       </c>
       <c r="D134" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="E134" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F134" t="s">
         <v>1344</v>
       </c>
       <c r="G134">
-        <v>6021</v>
+        <v>6001</v>
       </c>
       <c r="H134" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="135" spans="3:8" x14ac:dyDescent="0.2">
@@ -18468,19 +18777,19 @@
         <v>133</v>
       </c>
       <c r="D135" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="E135" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="F135" t="s">
         <v>1344</v>
       </c>
       <c r="G135">
-        <v>6031</v>
+        <v>6011</v>
       </c>
       <c r="H135" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="136" spans="3:8" x14ac:dyDescent="0.2">
@@ -18488,19 +18797,19 @@
         <v>134</v>
       </c>
       <c r="D136" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="E136" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="F136" t="s">
         <v>1344</v>
       </c>
       <c r="G136">
-        <v>6032</v>
+        <v>6021</v>
       </c>
       <c r="H136" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="137" spans="3:8" x14ac:dyDescent="0.2">
@@ -18508,19 +18817,19 @@
         <v>135</v>
       </c>
       <c r="D137" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E137" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="F137" t="s">
         <v>1344</v>
       </c>
       <c r="G137">
-        <v>6041</v>
+        <v>6031</v>
       </c>
       <c r="H137" t="s">
-        <v>1202</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="138" spans="3:8" x14ac:dyDescent="0.2">
@@ -18528,19 +18837,19 @@
         <v>136</v>
       </c>
       <c r="D138" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="E138" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="F138" t="s">
         <v>1344</v>
       </c>
       <c r="G138">
-        <v>6051</v>
+        <v>6032</v>
       </c>
       <c r="H138" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="139" spans="3:8" x14ac:dyDescent="0.2">
@@ -18548,19 +18857,19 @@
         <v>137</v>
       </c>
       <c r="D139" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="E139" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="F139" t="s">
         <v>1344</v>
       </c>
       <c r="G139">
-        <v>6061</v>
+        <v>6041</v>
       </c>
       <c r="H139" t="s">
-        <v>1359</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="140" spans="3:8" x14ac:dyDescent="0.2">
@@ -18568,16 +18877,16 @@
         <v>138</v>
       </c>
       <c r="D140" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="E140" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="F140" t="s">
         <v>1344</v>
       </c>
       <c r="G140">
-        <v>6101</v>
+        <v>6051</v>
       </c>
       <c r="H140" t="s">
         <v>1416</v>
@@ -18588,19 +18897,19 @@
         <v>139</v>
       </c>
       <c r="D141" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="E141" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="F141" t="s">
         <v>1344</v>
       </c>
       <c r="G141">
-        <v>6111</v>
+        <v>6061</v>
       </c>
       <c r="H141" t="s">
-        <v>1416</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="142" spans="3:8" x14ac:dyDescent="0.2">
@@ -18608,19 +18917,19 @@
         <v>140</v>
       </c>
       <c r="D142" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="E142" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="F142" t="s">
         <v>1344</v>
       </c>
       <c r="G142">
-        <v>6201</v>
+        <v>6101</v>
       </c>
       <c r="H142" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="143" spans="3:8" x14ac:dyDescent="0.2">
@@ -18628,19 +18937,19 @@
         <v>141</v>
       </c>
       <c r="D143" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="E143" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="F143" t="s">
         <v>1344</v>
       </c>
       <c r="G143">
-        <v>6202</v>
+        <v>6111</v>
       </c>
       <c r="H143" t="s">
-        <v>1112</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="144" spans="3:8" x14ac:dyDescent="0.2">
@@ -18648,16 +18957,16 @@
         <v>142</v>
       </c>
       <c r="D144" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="E144" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="F144" t="s">
         <v>1344</v>
       </c>
       <c r="G144">
-        <v>6203</v>
+        <v>6201</v>
       </c>
       <c r="H144" t="s">
         <v>1112</v>
@@ -18668,19 +18977,19 @@
         <v>143</v>
       </c>
       <c r="D145" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E145" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="F145" t="s">
         <v>1344</v>
       </c>
       <c r="G145">
-        <v>6301</v>
+        <v>6202</v>
       </c>
       <c r="H145" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="146" spans="3:8" x14ac:dyDescent="0.2">
@@ -18688,19 +18997,19 @@
         <v>144</v>
       </c>
       <c r="D146" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="E146" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="F146" t="s">
         <v>1344</v>
       </c>
       <c r="G146">
-        <v>6401</v>
+        <v>6203</v>
       </c>
       <c r="H146" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="147" spans="3:8" x14ac:dyDescent="0.2">
@@ -18708,16 +19017,16 @@
         <v>145</v>
       </c>
       <c r="D147" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E147" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="F147" t="s">
         <v>1344</v>
       </c>
       <c r="G147">
-        <v>6402</v>
+        <v>6301</v>
       </c>
       <c r="H147" t="s">
         <v>1416</v>
@@ -18728,16 +19037,16 @@
         <v>146</v>
       </c>
       <c r="D148" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="E148" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="F148" t="s">
         <v>1344</v>
       </c>
       <c r="G148">
-        <v>6405</v>
+        <v>6401</v>
       </c>
       <c r="H148" t="s">
         <v>1416</v>
@@ -18748,19 +19057,19 @@
         <v>147</v>
       </c>
       <c r="D149" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="E149" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="F149" t="s">
         <v>1344</v>
       </c>
       <c r="G149">
-        <v>6411</v>
+        <v>6402</v>
       </c>
       <c r="H149" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="150" spans="3:8" x14ac:dyDescent="0.2">
@@ -18768,19 +19077,19 @@
         <v>148</v>
       </c>
       <c r="D150" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="E150" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="F150" t="s">
         <v>1344</v>
       </c>
       <c r="G150">
-        <v>6421</v>
+        <v>6405</v>
       </c>
       <c r="H150" t="s">
-        <v>1094</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="151" spans="3:8" x14ac:dyDescent="0.2">
@@ -18788,19 +19097,19 @@
         <v>149</v>
       </c>
       <c r="D151" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="E151" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="F151" t="s">
         <v>1344</v>
       </c>
       <c r="G151">
-        <v>6501</v>
+        <v>6411</v>
       </c>
       <c r="H151" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="152" spans="3:8" x14ac:dyDescent="0.2">
@@ -18808,19 +19117,19 @@
         <v>150</v>
       </c>
       <c r="D152" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="E152" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="F152" t="s">
         <v>1344</v>
       </c>
       <c r="G152">
-        <v>6502</v>
+        <v>6421</v>
       </c>
       <c r="H152" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="153" spans="3:8" x14ac:dyDescent="0.2">
@@ -18828,16 +19137,16 @@
         <v>151</v>
       </c>
       <c r="D153" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="E153" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="F153" t="s">
         <v>1344</v>
       </c>
       <c r="G153">
-        <v>6511</v>
+        <v>6501</v>
       </c>
       <c r="H153" t="s">
         <v>1112</v>
@@ -18848,16 +19157,16 @@
         <v>152</v>
       </c>
       <c r="D154" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="E154" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="F154" t="s">
         <v>1344</v>
       </c>
       <c r="G154">
-        <v>6521</v>
+        <v>6502</v>
       </c>
       <c r="H154" t="s">
         <v>1112</v>
@@ -18868,16 +19177,16 @@
         <v>153</v>
       </c>
       <c r="D155" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="E155" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="F155" t="s">
         <v>1344</v>
       </c>
       <c r="G155">
-        <v>6531</v>
+        <v>6511</v>
       </c>
       <c r="H155" t="s">
         <v>1112</v>
@@ -18888,16 +19197,16 @@
         <v>154</v>
       </c>
       <c r="D156" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="E156" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="F156" t="s">
         <v>1344</v>
       </c>
       <c r="G156">
-        <v>6541</v>
+        <v>6521</v>
       </c>
       <c r="H156" t="s">
         <v>1112</v>
@@ -18908,16 +19217,16 @@
         <v>155</v>
       </c>
       <c r="D157" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="E157" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="F157" t="s">
         <v>1344</v>
       </c>
       <c r="G157">
-        <v>6542</v>
+        <v>6531</v>
       </c>
       <c r="H157" t="s">
         <v>1112</v>
@@ -18928,19 +19237,19 @@
         <v>156</v>
       </c>
       <c r="D158" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="E158" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="F158" t="s">
         <v>1344</v>
       </c>
       <c r="G158">
-        <v>6601</v>
+        <v>6541</v>
       </c>
       <c r="H158" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="159" spans="3:8" x14ac:dyDescent="0.2">
@@ -18948,19 +19257,19 @@
         <v>157</v>
       </c>
       <c r="D159" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="E159" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="F159" t="s">
         <v>1344</v>
       </c>
       <c r="G159">
-        <v>6602</v>
+        <v>6542</v>
       </c>
       <c r="H159" t="s">
-        <v>1416</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="160" spans="3:8" x14ac:dyDescent="0.2">
@@ -18968,16 +19277,16 @@
         <v>158</v>
       </c>
       <c r="D160" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="E160" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="F160" t="s">
         <v>1344</v>
       </c>
       <c r="G160">
-        <v>6603</v>
+        <v>6601</v>
       </c>
       <c r="H160" t="s">
         <v>1416</v>
@@ -18988,16 +19297,16 @@
         <v>159</v>
       </c>
       <c r="D161" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="E161" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="F161" t="s">
         <v>1344</v>
       </c>
       <c r="G161">
-        <v>6604</v>
+        <v>6602</v>
       </c>
       <c r="H161" t="s">
         <v>1416</v>
@@ -19008,16 +19317,16 @@
         <v>160</v>
       </c>
       <c r="D162" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="E162" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="F162" t="s">
         <v>1344</v>
       </c>
       <c r="G162">
-        <v>6701</v>
+        <v>6603</v>
       </c>
       <c r="H162" t="s">
         <v>1416</v>
@@ -19028,16 +19337,16 @@
         <v>161</v>
       </c>
       <c r="D163" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="E163" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="F163" t="s">
         <v>1344</v>
       </c>
       <c r="G163">
-        <v>6711</v>
+        <v>6604</v>
       </c>
       <c r="H163" t="s">
         <v>1416</v>
@@ -19048,16 +19357,16 @@
         <v>162</v>
       </c>
       <c r="D164" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="E164" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="F164" t="s">
         <v>1344</v>
       </c>
       <c r="G164">
-        <v>6801</v>
+        <v>6701</v>
       </c>
       <c r="H164" t="s">
         <v>1416</v>
@@ -19068,18 +19377,58 @@
         <v>163</v>
       </c>
       <c r="D165" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="E165" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="F165" t="s">
         <v>1344</v>
       </c>
       <c r="G165">
+        <v>6711</v>
+      </c>
+      <c r="H165" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="166" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C166">
+        <v>164</v>
+      </c>
+      <c r="D166" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E166" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F166" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G166">
+        <v>6801</v>
+      </c>
+      <c r="H166" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="167" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C167">
+        <v>165</v>
+      </c>
+      <c r="D167" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E167" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F167" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G167">
         <v>6901</v>
       </c>
-      <c r="H165" t="s">
+      <c r="H167" t="s">
         <v>1416</v>
       </c>
     </row>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F23793-2B98-4C6C-A9C5-F6D98CBFBA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCF045C-3CCF-4761-BC64-9D4D5D0DCF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4905,10 +4905,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ORDER0001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LONG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4925,10 +4921,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>order_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1#策略/普通订单/长头/借/在途物资</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5448,10 +5440,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ORDER0002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">3#策略/普通订单/长头/借/银行存款 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5468,10 +5456,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ORDER0003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3#策略/发货单/长头/借/发出商品</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5664,6 +5648,19 @@
   <si>
     <t>1000#策略/持有至到期投资-到期处置/长头/借/持有至到期投资-成本</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bill_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BILL0001</t>
+  </si>
+  <si>
+    <t>BILL0003</t>
+  </si>
+  <si>
+    <t>BILL0002</t>
   </si>
 </sst>
 </file>
@@ -5811,7 +5808,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -5826,7 +5823,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11720,7 +11716,7 @@
         <v>999</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1482</v>
+        <v>1698</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>1476</v>
@@ -11740,22 +11736,22 @@
         <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>1478</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>1479</v>
       </c>
       <c r="H3" s="4">
         <v>1402</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.2">
@@ -11763,22 +11759,22 @@
         <v>2</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>1478</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H4" s="4">
         <v>1002</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.2">
@@ -11786,22 +11782,22 @@
         <v>3</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1477</v>
+        <v>1699</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H5" s="4">
         <v>1407</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.2">
@@ -11809,22 +11805,22 @@
         <v>4</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1477</v>
+        <v>1699</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H6" s="4">
         <v>1406</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.2">
@@ -11832,22 +11828,22 @@
         <v>5</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>1478</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>1479</v>
       </c>
       <c r="H7" s="4">
         <v>1402</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.2">
@@ -11855,22 +11851,22 @@
         <v>6</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>1477</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>1478</v>
-      </c>
       <c r="G8" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H8" s="4">
         <v>1002</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.2">
@@ -11878,22 +11874,22 @@
         <v>7</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1477</v>
+        <v>1699</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H9" s="4">
         <v>1122</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="10" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -11901,22 +11897,22 @@
         <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1477</v>
+        <v>1699</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H10" s="8">
         <v>6001</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.2">
@@ -11924,22 +11920,22 @@
         <v>9</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>1477</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>1478</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>1479</v>
       </c>
       <c r="H11" s="7">
         <v>1002</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>1649</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.2">
@@ -11947,22 +11943,22 @@
         <v>10</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>1478</v>
-      </c>
       <c r="G12" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H12" s="5">
         <v>6001</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>1650</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.2">
@@ -11970,22 +11966,22 @@
         <v>11</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1651</v>
+        <v>1700</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>1478</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>1479</v>
       </c>
       <c r="H13" s="5">
         <v>1407</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>1654</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.2">
@@ -11993,22 +11989,22 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1651</v>
+        <v>1700</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H14" s="5">
         <v>1406</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>1655</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.2">
@@ -12016,22 +12012,22 @@
         <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1477</v>
+        <v>1699</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H15" s="4">
         <v>1002</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>1647</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.2">
@@ -12039,22 +12035,22 @@
         <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1477</v>
+        <v>1699</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H16" s="4">
         <v>6001</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>1648</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.2">
@@ -12062,22 +12058,22 @@
         <v>15</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1646</v>
+        <v>1701</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H17" s="4">
         <v>1407</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>1652</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.2">
@@ -12085,22 +12081,22 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1646</v>
+        <v>1701</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H18" s="4">
         <v>1406</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>1653</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.2">
@@ -12108,22 +12104,22 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1651</v>
+        <v>1700</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H19" s="4">
         <v>6401</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -12131,22 +12127,22 @@
         <v>18</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1651</v>
+        <v>1700</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H20" s="8">
         <v>1406</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>1656</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.2">
@@ -12154,22 +12150,22 @@
         <v>19</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="F21" s="11" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G21" s="11" t="s">
         <v>1478</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>1479</v>
       </c>
       <c r="H21" s="11">
         <v>11010001</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.2">
@@ -12177,22 +12173,22 @@
         <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>1478</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>1479</v>
       </c>
       <c r="H22" s="5">
         <v>1131</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.2">
@@ -12200,22 +12196,22 @@
         <v>21</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="F23" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>1478</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>1479</v>
       </c>
       <c r="H23" s="5">
         <v>6111</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.2">
@@ -12223,22 +12219,22 @@
         <v>22</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1675</v>
+        <v>1671</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H24" s="5">
         <v>1002</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.2">
@@ -12246,22 +12242,22 @@
         <v>23</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="F25" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>1478</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>1479</v>
       </c>
       <c r="H25" s="4">
         <v>1002</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.2">
@@ -12269,22 +12265,22 @@
         <v>24</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H26" s="4">
         <v>1131</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.2">
@@ -12292,22 +12288,22 @@
         <v>25</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="F27" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>1478</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>1479</v>
       </c>
       <c r="H27" s="5">
         <v>11010002</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>1669</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.2">
@@ -12315,22 +12311,22 @@
         <v>26</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H28" s="5">
         <v>6101</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.2">
@@ -12338,22 +12334,22 @@
         <v>27</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>1478</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>1479</v>
       </c>
       <c r="H29" s="4">
         <v>1002</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>1680</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.2">
@@ -12361,22 +12357,22 @@
         <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="H30" s="4">
         <v>6101</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>1672</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.2">
@@ -12384,22 +12380,22 @@
         <v>29</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="H31" s="4">
         <v>11010001</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>1673</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.2">
@@ -12407,22 +12403,22 @@
         <v>30</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="H32" s="13">
         <v>11010002</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>1674</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.2">
@@ -12430,22 +12426,22 @@
         <v>31</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="H33" s="13">
         <v>6111</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>1679</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.2">
@@ -12453,22 +12449,22 @@
         <v>32</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
       <c r="F34" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>1478</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>1479</v>
       </c>
       <c r="H34" s="5">
         <v>15210001</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.2">
@@ -12476,22 +12472,22 @@
         <v>33</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1670</v>
+        <v>1666</v>
       </c>
       <c r="H35" s="5">
         <v>15210002</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>1690</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.2">
@@ -12499,22 +12495,22 @@
         <v>34</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>1658</v>
+        <v>1654</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H36" s="5">
         <v>1002</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.2">
@@ -12522,22 +12518,22 @@
         <v>35</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="H37" s="4">
         <v>15210001</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>1693</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.2">
@@ -12545,22 +12541,22 @@
         <v>36</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="H38" s="4">
         <v>15210002</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.2">
@@ -12568,22 +12564,22 @@
         <v>37</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>1697</v>
+        <v>1693</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>1686</v>
+        <v>1682</v>
       </c>
       <c r="H39" s="4">
         <v>6111</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.2">
@@ -12591,22 +12587,22 @@
         <v>38</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="H40" s="5">
         <v>1002</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.2">
@@ -12614,68 +12610,68 @@
         <v>39</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>1698</v>
+        <v>1694</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H41" s="5">
         <v>1132</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>1696</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C42" s="14">
+      <c r="C42" s="4">
         <v>40</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>1699</v>
+        <v>1695</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="H42" s="4">
         <v>1002</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>1700</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.2">
-      <c r="C43" s="14">
+      <c r="C43" s="4">
         <v>41</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>1699</v>
+        <v>1695</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>1671</v>
+        <v>1667</v>
       </c>
       <c r="H43" s="4">
         <v>1002</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>1701</v>
+        <v>1697</v>
       </c>
     </row>
   </sheetData>
@@ -12706,7 +12702,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
@@ -12714,7 +12710,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
@@ -12722,7 +12718,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
@@ -12730,7 +12726,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
@@ -12738,7 +12734,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
@@ -12746,7 +12742,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
     </row>
   </sheetData>
@@ -13859,22 +13855,22 @@
         <v>998</v>
       </c>
       <c r="C2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E2" t="s">
         <v>1630</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1632</v>
       </c>
       <c r="F2" t="s">
         <v>1417</v>
       </c>
       <c r="G2" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="H2" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="I2" t="s">
         <v>1037</v>
@@ -13894,13 +13890,13 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -13909,7 +13905,7 @@
         <v>45291.529166666667</v>
       </c>
       <c r="J3" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
     </row>
   </sheetData>
@@ -13963,7 +13959,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>40926.496965423699</v>
+        <v>44661.324730875916</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -13988,7 +13984,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>40520.280178656205</v>
+        <v>36140.768682737478</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -14013,7 +14009,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38107.782219386296</v>
+        <v>45054.393283509547</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -14038,7 +14034,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40459.557431692112</v>
+        <v>38334.778547495087</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -14063,7 +14059,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44653.680435386668</v>
+        <v>44357.53302623691</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -14088,7 +14084,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41844.316229127668</v>
+        <v>38030.829066624545</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -14113,7 +14109,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39185.304680449022</v>
+        <v>36684.183917015558</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -14138,7 +14134,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41974.535348533238</v>
+        <v>37928.765914967124</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -14163,7 +14159,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45104.668034847869</v>
+        <v>42761.269853200603</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -14188,7 +14184,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38644.253369335856</v>
+        <v>38894.726074763341</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -14213,7 +14209,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44898.359436510029</v>
+        <v>36636.440492026071</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -14238,7 +14234,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44991.569935888845</v>
+        <v>40151.340231135648</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -14263,7 +14259,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42336.543804867448</v>
+        <v>44994.965738163839</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -14288,7 +14284,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38677.342438012965</v>
+        <v>36426.434129737441</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -14313,7 +14309,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38925.508798756033</v>
+        <v>39415.614485986414</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -14338,7 +14334,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41342.154797522737</v>
+        <v>37696.712862253349</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -14363,7 +14359,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44292.107325674115</v>
+        <v>38632.146144290338</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -14388,7 +14384,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36102.61652407088</v>
+        <v>43086.867830339739</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -14413,7 +14409,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41324.969808373193</v>
+        <v>41997.777296553715</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -14438,7 +14434,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39479.904782327823</v>
+        <v>40449.835630422145</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -14463,7 +14459,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36376.868241241013</v>
+        <v>37927.711663391347</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -14488,7 +14484,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42189.556548641805</v>
+        <v>39093.476815349713</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -14513,7 +14509,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38928.897679568647</v>
+        <v>43584.285195570497</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -14538,7 +14534,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43195.560745696501</v>
+        <v>36262.448322953351</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -14563,7 +14559,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38256.163723931735</v>
+        <v>42667.01330628604</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -14588,7 +14584,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38486.296590376187</v>
+        <v>41631.193269291252</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -14613,7 +14609,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39672.506993358853</v>
+        <v>41716.862927754912</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -14638,7 +14634,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43054.10866466639</v>
+        <v>43967.366703320571</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -14663,7 +14659,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39234.389292513188</v>
+        <v>38796.286344776192</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -14688,7 +14684,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42295.59702522571</v>
+        <v>42704.409366010652</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -14743,16 +14739,16 @@
         <v>1039</v>
       </c>
       <c r="F2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H2" t="s">
         <v>1624</v>
       </c>
-      <c r="G2" t="s">
-        <v>1492</v>
-      </c>
-      <c r="H2" t="s">
-        <v>1626</v>
-      </c>
       <c r="I2" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="J2" t="s">
         <v>1078</v>
@@ -14763,28 +14759,28 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D3">
         <v>123456</v>
       </c>
       <c r="E3" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F3">
         <v>18601494620</v>
       </c>
       <c r="G3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1495</v>
+      </c>
+      <c r="I3" t="s">
         <v>1496</v>
       </c>
-      <c r="H3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="I3" t="s">
-        <v>1498</v>
-      </c>
       <c r="J3" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.2">
@@ -14792,28 +14788,28 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="D4">
         <v>123456</v>
       </c>
       <c r="E4" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F4">
         <v>18601494621</v>
       </c>
       <c r="G4" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="H4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J4" t="s">
         <v>1497</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1501</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.2">
@@ -14821,28 +14817,28 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="D5">
         <v>123456</v>
       </c>
       <c r="E5" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F5">
         <v>18601494622</v>
       </c>
       <c r="G5" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H5" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="I5" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="J5" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.2">
@@ -14850,28 +14846,28 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="D6">
         <v>123456</v>
       </c>
       <c r="E6" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F6">
         <v>18601494623</v>
       </c>
       <c r="G6" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H6" t="s">
+        <v>1501</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1505</v>
+      </c>
+      <c r="J6" t="s">
         <v>1503</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1507</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -14879,28 +14875,28 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="D7">
         <v>123456</v>
       </c>
       <c r="E7" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F7">
         <v>18601494624</v>
       </c>
       <c r="G7" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H7" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="I7" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="J7" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -14908,28 +14904,28 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="D8">
         <v>123456</v>
       </c>
       <c r="E8" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F8">
         <v>18601494625</v>
       </c>
       <c r="G8" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="H8" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="I8" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="J8" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
@@ -14937,28 +14933,28 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="D9">
         <v>123456</v>
       </c>
       <c r="E9" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F9">
         <v>18601494626</v>
       </c>
       <c r="G9" t="s">
+        <v>1513</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I9" t="s">
         <v>1515</v>
       </c>
-      <c r="H9" t="s">
-        <v>1516</v>
-      </c>
-      <c r="I9" t="s">
-        <v>1517</v>
-      </c>
       <c r="J9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
@@ -14966,28 +14962,28 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D10">
         <v>123456</v>
       </c>
       <c r="E10" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F10">
         <v>18601494627</v>
       </c>
       <c r="G10" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="H10" t="s">
+        <v>1514</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J10" t="s">
         <v>1516</v>
-      </c>
-      <c r="I10" t="s">
-        <v>1521</v>
-      </c>
-      <c r="J10" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
@@ -14995,28 +14991,28 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D11">
         <v>123456</v>
       </c>
       <c r="E11" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F11">
         <v>18601494628</v>
       </c>
       <c r="G11" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H11" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="I11" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="J11" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -15024,28 +15020,28 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="D12">
         <v>123456</v>
       </c>
       <c r="E12" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F12">
         <v>18601494629</v>
       </c>
       <c r="G12" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1525</v>
+      </c>
+      <c r="J12" t="s">
         <v>1523</v>
-      </c>
-      <c r="I12" t="s">
-        <v>1527</v>
-      </c>
-      <c r="J12" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
@@ -15053,28 +15049,28 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="D13">
         <v>123456</v>
       </c>
       <c r="E13" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F13">
         <v>18601494630</v>
       </c>
       <c r="G13" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="H13" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I13" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="J13" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
@@ -15082,28 +15078,28 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="D14">
         <v>123456</v>
       </c>
       <c r="E14" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F14">
         <v>18601494631</v>
       </c>
       <c r="G14" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H14" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="I14" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="J14" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
@@ -15111,28 +15107,28 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="D15">
         <v>123456</v>
       </c>
       <c r="E15" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F15">
         <v>18601494632</v>
       </c>
       <c r="G15" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="H15" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="I15" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="J15" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
@@ -15140,28 +15136,28 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="D16">
         <v>123456</v>
       </c>
       <c r="E16" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F16">
         <v>18601494633</v>
       </c>
       <c r="G16" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="H16" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I16" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="J16" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.2">
@@ -15169,28 +15165,28 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="D17">
         <v>123456</v>
       </c>
       <c r="E17" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F17">
         <v>18601494634</v>
       </c>
       <c r="G17" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="H17" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I17" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="J17" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.2">
@@ -15198,28 +15194,28 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="D18">
         <v>123456</v>
       </c>
       <c r="E18" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F18">
         <v>18601494635</v>
       </c>
       <c r="G18" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1543</v>
+      </c>
+      <c r="I18" t="s">
         <v>1544</v>
       </c>
-      <c r="H18" t="s">
-        <v>1545</v>
-      </c>
-      <c r="I18" t="s">
-        <v>1546</v>
-      </c>
       <c r="J18" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.2">
@@ -15227,28 +15223,28 @@
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="D19">
         <v>123456</v>
       </c>
       <c r="E19" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F19">
         <v>18601494636</v>
       </c>
       <c r="G19" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="H19" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="I19" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="J19" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.2">
@@ -15256,28 +15252,28 @@
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D20">
         <v>123456</v>
       </c>
       <c r="E20" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F20">
         <v>18601494637</v>
       </c>
       <c r="G20" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H20" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I20" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="J20" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.2">
@@ -15285,28 +15281,28 @@
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="D21">
         <v>123456</v>
       </c>
       <c r="E21" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F21">
         <v>18601494638</v>
       </c>
       <c r="G21" t="s">
+        <v>1549</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1543</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1552</v>
+      </c>
+      <c r="J21" t="s">
         <v>1551</v>
-      </c>
-      <c r="H21" t="s">
-        <v>1545</v>
-      </c>
-      <c r="I21" t="s">
-        <v>1554</v>
-      </c>
-      <c r="J21" t="s">
-        <v>1553</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.2">
@@ -15314,28 +15310,28 @@
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="D22">
         <v>123456</v>
       </c>
       <c r="E22" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F22">
         <v>18601494639</v>
       </c>
       <c r="G22" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H22" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I22" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="J22" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.2">
@@ -15343,28 +15339,28 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="D23">
         <v>123456</v>
       </c>
       <c r="E23" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F23">
         <v>18601494640</v>
       </c>
       <c r="G23" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="H23" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I23" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="J23" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.2">
@@ -15372,28 +15368,28 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="D24">
         <v>123456</v>
       </c>
       <c r="E24" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F24">
         <v>18601494641</v>
       </c>
       <c r="G24" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="H24" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I24" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="J24" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.2">
@@ -15401,28 +15397,28 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="D25">
         <v>123456</v>
       </c>
       <c r="E25" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F25">
         <v>18601494642</v>
       </c>
       <c r="G25" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H25" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I25" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="J25" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.2">
@@ -15430,28 +15426,28 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="D26">
         <v>123456</v>
       </c>
       <c r="E26" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F26">
         <v>18601494643</v>
       </c>
       <c r="G26" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="H26" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I26" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="J26" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.2">
@@ -15459,28 +15455,28 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="D27">
         <v>123456</v>
       </c>
       <c r="E27" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F27">
         <v>18601494644</v>
       </c>
       <c r="G27" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H27" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I27" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="J27" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.2">
@@ -15488,28 +15484,28 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D28">
         <v>123456</v>
       </c>
       <c r="E28" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F28">
         <v>18601494645</v>
       </c>
       <c r="G28" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="H28" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I28" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="J28" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.2">
@@ -15517,28 +15513,28 @@
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="D29">
         <v>123456</v>
       </c>
       <c r="E29" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F29">
         <v>18601494646</v>
       </c>
       <c r="G29" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H29" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I29" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="J29" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.2">
@@ -15546,28 +15542,28 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="D30">
         <v>123456</v>
       </c>
       <c r="E30" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F30">
         <v>18601494647</v>
       </c>
       <c r="G30" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="H30" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I30" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="J30" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.2">
@@ -15575,28 +15571,28 @@
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="D31">
         <v>123456</v>
       </c>
       <c r="E31" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F31">
         <v>18601494648</v>
       </c>
       <c r="G31" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="H31" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I31" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="J31" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.2">
@@ -15604,28 +15600,28 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="D32">
         <v>123456</v>
       </c>
       <c r="E32" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F32">
         <v>18601494649</v>
       </c>
       <c r="G32" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="H32" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I32" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="J32" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.2">
@@ -15633,28 +15629,28 @@
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D33">
         <v>123456</v>
       </c>
       <c r="E33" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F33">
         <v>18601494650</v>
       </c>
       <c r="G33" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="H33" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I33" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="J33" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.2">
@@ -15662,28 +15658,28 @@
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D34">
         <v>123456</v>
       </c>
       <c r="E34" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F34">
         <v>18601494651</v>
       </c>
       <c r="G34" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="H34" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I34" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="J34" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.2">
@@ -15691,28 +15687,28 @@
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="D35">
         <v>123456</v>
       </c>
       <c r="E35" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F35">
         <v>18601494652</v>
       </c>
       <c r="G35" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="H35" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I35" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="J35" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.2">
@@ -15720,28 +15716,28 @@
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="D36">
         <v>123456</v>
       </c>
       <c r="E36" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F36">
         <v>18601494653</v>
       </c>
       <c r="G36" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="H36" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I36" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="J36" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.2">
@@ -15749,28 +15745,28 @@
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="D37">
         <v>123456</v>
       </c>
       <c r="E37" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F37">
         <v>18601494654</v>
       </c>
       <c r="G37" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="H37" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I37" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="J37" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.2">
@@ -15778,28 +15774,28 @@
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="D38">
         <v>123456</v>
       </c>
       <c r="E38" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F38">
         <v>18601494655</v>
       </c>
       <c r="G38" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="H38" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I38" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="J38" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.2">
@@ -15807,28 +15803,28 @@
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D39">
         <v>123456</v>
       </c>
       <c r="E39" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F39">
         <v>18601494656</v>
       </c>
       <c r="G39" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="H39" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I39" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="J39" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.2">
@@ -15836,28 +15832,28 @@
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="D40">
         <v>123456</v>
       </c>
       <c r="E40" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F40">
         <v>18601494657</v>
       </c>
       <c r="G40" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="H40" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I40" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="J40" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.2">
@@ -15865,28 +15861,28 @@
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="D41">
         <v>123456</v>
       </c>
       <c r="E41" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F41">
         <v>18601494658</v>
       </c>
       <c r="G41" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="H41" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I41" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="J41" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.2">
@@ -15894,28 +15890,28 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="D42">
         <v>123456</v>
       </c>
       <c r="E42" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F42">
         <v>18601494659</v>
       </c>
       <c r="G42" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="H42" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I42" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="J42" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.2">
@@ -15923,28 +15919,28 @@
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="D43">
         <v>123456</v>
       </c>
       <c r="E43" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F43">
         <v>18601494660</v>
       </c>
       <c r="G43" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="H43" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I43" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="J43" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.2">
@@ -15952,28 +15948,28 @@
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="D44">
         <v>123456</v>
       </c>
       <c r="E44" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F44">
         <v>18601494661</v>
       </c>
       <c r="G44" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="H44" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I44" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="J44" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.2">
@@ -15981,28 +15977,28 @@
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="D45">
         <v>123456</v>
       </c>
       <c r="E45" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F45">
         <v>18601494662</v>
       </c>
       <c r="G45" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="H45" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I45" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="J45" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.2">
@@ -16010,28 +16006,28 @@
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="D46">
         <v>123456</v>
       </c>
       <c r="E46" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F46">
         <v>18601494663</v>
       </c>
       <c r="G46" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="H46" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I46" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="J46" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.2">
@@ -16039,28 +16035,28 @@
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="D47">
         <v>123456</v>
       </c>
       <c r="E47" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F47">
         <v>18601494664</v>
       </c>
       <c r="G47" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="H47" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="I47" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="J47" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.2">
@@ -16068,28 +16064,28 @@
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="D48">
         <v>123456</v>
       </c>
       <c r="E48" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="F48">
         <v>18601494665</v>
       </c>
       <c r="G48" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="H48" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="I48" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="J48" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
     </row>
   </sheetData>
@@ -16317,10 +16313,10 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="E12" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
       <c r="F12" t="s">
         <v>1081</v>
@@ -16337,10 +16333,10 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="E13" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="F13" t="s">
         <v>1081</v>
@@ -17057,7 +17053,7 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
       <c r="E49" t="s">
         <v>1171</v>
@@ -17077,7 +17073,7 @@
         <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
       <c r="E50" t="s">
         <v>1171</v>

--- a/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
+++ b/src/test/java/gbench/sandbox/jdbc/finance/acct/acct_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\sandbox\jdbc\finance\acct\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCF045C-3CCF-4761-BC64-9D4D5D0DCF8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA624E3-CF8F-4E14-BAC3-EF5DB4F620C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_company" sheetId="1" r:id="rId1"/>
@@ -5404,10 +5404,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"items":[{"id":1,"price":1.0,"quantity":1.0,"amount":1.0},{"id":2,"price":1.0,"quantity":1.0,"amount":1.0}]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>上海大云中转仓库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5661,6 +5657,10 @@
   </si>
   <si>
     <t>BILL0002</t>
+  </si>
+  <si>
+    <t>{"items":[{"id":11,"price":1.0,"quantity":1.0,"amount":1.0},{"id":12,"price":1.0,"quantity":1.0,"amount":1.0}]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11716,7 +11716,7 @@
         <v>999</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>1476</v>
@@ -11739,7 +11739,7 @@
         <v>1488</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>1477</v>
@@ -11762,7 +11762,7 @@
         <v>1488</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>1477</v>
@@ -11785,7 +11785,7 @@
         <v>1488</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>1480</v>
@@ -11808,7 +11808,7 @@
         <v>1488</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1480</v>
@@ -11831,7 +11831,7 @@
         <v>1489</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>1477</v>
@@ -11854,7 +11854,7 @@
         <v>1489</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>1477</v>
@@ -11877,7 +11877,7 @@
         <v>1489</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1480</v>
@@ -11897,10 +11897,10 @@
         <v>8</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>1480</v>
@@ -11920,10 +11920,10 @@
         <v>9</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>1477</v>
@@ -11935,7 +11935,7 @@
         <v>1002</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.2">
@@ -11943,10 +11943,10 @@
         <v>10</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>1477</v>
@@ -11958,7 +11958,7 @@
         <v>6001</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.2">
@@ -11966,10 +11966,10 @@
         <v>11</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>1477</v>
@@ -11981,7 +11981,7 @@
         <v>1407</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.2">
@@ -11989,10 +11989,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>1477</v>
@@ -12004,7 +12004,7 @@
         <v>1406</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.2">
@@ -12012,10 +12012,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>1480</v>
@@ -12027,7 +12027,7 @@
         <v>1002</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.2">
@@ -12035,10 +12035,10 @@
         <v>14</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>1480</v>
@@ -12050,7 +12050,7 @@
         <v>6001</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.2">
@@ -12058,10 +12058,10 @@
         <v>15</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>1480</v>
@@ -12073,7 +12073,7 @@
         <v>1407</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.2">
@@ -12081,10 +12081,10 @@
         <v>16</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>1480</v>
@@ -12096,7 +12096,7 @@
         <v>1406</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.2">
@@ -12104,10 +12104,10 @@
         <v>17</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>1480</v>
@@ -12119,7 +12119,7 @@
         <v>6401</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="20" spans="3:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -12127,10 +12127,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>1480</v>
@@ -12142,7 +12142,7 @@
         <v>1406</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.2">
@@ -12150,10 +12150,10 @@
         <v>19</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>1477</v>
@@ -12165,7 +12165,7 @@
         <v>11010001</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.2">
@@ -12173,10 +12173,10 @@
         <v>20</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>1477</v>
@@ -12188,7 +12188,7 @@
         <v>1131</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.2">
@@ -12196,10 +12196,10 @@
         <v>21</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>1477</v>
@@ -12211,7 +12211,7 @@
         <v>6111</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.2">
@@ -12219,10 +12219,10 @@
         <v>22</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>1477</v>
@@ -12234,7 +12234,7 @@
         <v>1002</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.2">
@@ -12242,10 +12242,10 @@
         <v>23</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>1477</v>
@@ -12257,7 +12257,7 @@
         <v>1002</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.2">
@@ -12265,10 +12265,10 @@
         <v>24</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>1477</v>
@@ -12280,7 +12280,7 @@
         <v>1131</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="27" spans="3:9" x14ac:dyDescent="0.2">
@@ -12288,10 +12288,10 @@
         <v>25</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>1477</v>
@@ -12303,7 +12303,7 @@
         <v>11010002</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="28" spans="3:9" x14ac:dyDescent="0.2">
@@ -12311,10 +12311,10 @@
         <v>26</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>1477</v>
@@ -12326,7 +12326,7 @@
         <v>6101</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="29" spans="3:9" x14ac:dyDescent="0.2">
@@ -12334,10 +12334,10 @@
         <v>27</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>1477</v>
@@ -12349,7 +12349,7 @@
         <v>1002</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="30" spans="3:9" x14ac:dyDescent="0.2">
@@ -12357,22 +12357,22 @@
         <v>28</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1477</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H30" s="4">
         <v>6101</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="31" spans="3:9" x14ac:dyDescent="0.2">
@@ -12380,22 +12380,22 @@
         <v>29</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>1477</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H31" s="4">
         <v>11010001</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="32" spans="3:9" x14ac:dyDescent="0.2">
@@ -12403,22 +12403,22 @@
         <v>30</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>1477</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H32" s="13">
         <v>11010002</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.2">
@@ -12426,22 +12426,22 @@
         <v>31</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>1477</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H33" s="13">
         <v>6111</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.2">
@@ -12449,10 +12449,10 @@
         <v>32</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>1477</v>
@@ -12464,7 +12464,7 @@
         <v>15210001</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.2">
@@ -12472,22 +12472,22 @@
         <v>33</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>1477</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H35" s="5">
         <v>15210002</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.2">
@@ -12495,10 +12495,10 @@
         <v>34</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>1477</v>
@@ -12510,7 +12510,7 @@
         <v>1002</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.2">
@@ -12518,22 +12518,22 @@
         <v>35</v>
       </c>
       <c r="D37" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>1687</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>1693</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>1688</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H37" s="4">
         <v>15210001</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.2">
@@ -12541,22 +12541,22 @@
         <v>36</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>1687</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>1693</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>1688</v>
-      </c>
       <c r="G38" s="4" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H38" s="4">
         <v>15210002</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.2">
@@ -12564,22 +12564,22 @@
         <v>37</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>1687</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>1693</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>1688</v>
-      </c>
       <c r="G39" s="4" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H39" s="4">
         <v>6111</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.2">
@@ -12587,22 +12587,22 @@
         <v>38</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>1687</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>1694</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>1688</v>
-      </c>
       <c r="G40" s="5" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H40" s="5">
         <v>1002</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.2">
@@ -12610,13 +12610,13 @@
         <v>39</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>1687</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>1694</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>1688</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>1479</v>
@@ -12625,7 +12625,7 @@
         <v>1132</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.2">
@@ -12633,22 +12633,22 @@
         <v>40</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>1687</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>1695</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>1688</v>
-      </c>
       <c r="G42" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H42" s="4">
         <v>1002</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.2">
@@ -12656,22 +12656,22 @@
         <v>41</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>1686</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>1687</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>1695</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>1688</v>
-      </c>
       <c r="G43" s="4" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H43" s="4">
         <v>1002</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
   </sheetData>
@@ -12702,7 +12702,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
@@ -12710,7 +12710,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
@@ -12718,7 +12718,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
@@ -12726,7 +12726,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
@@ -12734,7 +12734,7 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
@@ -12742,7 +12742,7 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
   </sheetData>
@@ -13890,7 +13890,7 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>1635</v>
+        <v>1701</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="E3" s="2">
         <f ca="1">NOW()-RAND()*10000</f>
-        <v>44661.324730875916</v>
+        <v>36784.003681424882</v>
       </c>
       <c r="F3">
         <v>123456</v>
@@ -13984,7 +13984,7 @@
       </c>
       <c r="E4" s="2">
         <f t="shared" ref="E4:E32" ca="1" si="0">NOW()-RAND()*10000</f>
-        <v>36140.768682737478</v>
+        <v>36373.226474313386</v>
       </c>
       <c r="F4">
         <v>123456</v>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="E5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>45054.393283509547</v>
+        <v>43160.763866239875</v>
       </c>
       <c r="F5">
         <v>123456</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="E6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38334.778547495087</v>
+        <v>40093.965654657863</v>
       </c>
       <c r="F6">
         <v>123456</v>
@@ -14059,7 +14059,7 @@
       </c>
       <c r="E7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44357.53302623691</v>
+        <v>39087.736731862096</v>
       </c>
       <c r="F7">
         <v>123456</v>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38030.829066624545</v>
+        <v>38429.895644254975</v>
       </c>
       <c r="F8">
         <v>123456</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36684.183917015558</v>
+        <v>42996.208432401218</v>
       </c>
       <c r="F9">
         <v>123456</v>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37928.765914967124</v>
+        <v>43055.652674296078</v>
       </c>
       <c r="F10">
         <v>123456</v>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="E11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42761.269853200603</v>
+        <v>36863.283924640833</v>
       </c>
       <c r="F11">
         <v>123456</v>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="E12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38894.726074763341</v>
+        <v>44703.573546743879</v>
       </c>
       <c r="F12">
         <v>123456</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="E13" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36636.440492026071</v>
+        <v>38724.55374362586</v>
       </c>
       <c r="F13">
         <v>123456</v>
@@ -14234,7 +14234,7 @@
       </c>
       <c r="E14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40151.340231135648</v>
+        <v>38440.724241559765</v>
       </c>
       <c r="F14">
         <v>123456</v>
@@ -14259,7 +14259,7 @@
       </c>
       <c r="E15" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>44994.965738163839</v>
+        <v>41640.791335557209</v>
       </c>
       <c r="F15">
         <v>123456</v>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="E16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36426.434129737441</v>
+        <v>36288.532807063137</v>
       </c>
       <c r="F16">
         <v>123456</v>
@@ -14309,7 +14309,7 @@
       </c>
       <c r="E17" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39415.614485986414</v>
+        <v>41487.853696608952</v>
       </c>
       <c r="F17">
         <v>123456</v>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="E18" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37696.712862253349</v>
+        <v>36166.619159813083</v>
       </c>
       <c r="F18">
         <v>123456</v>
@@ -14359,7 +14359,7 @@
       </c>
       <c r="E19" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38632.146144290338</v>
+        <v>35902.169732759969</v>
       </c>
       <c r="F19">
         <v>123456</v>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="E20" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43086.867830339739</v>
+        <v>38378.794529409839</v>
       </c>
       <c r="F20">
         <v>123456</v>
@@ -14409,7 +14409,7 @@
       </c>
       <c r="E21" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41997.777296553715</v>
+        <v>36830.268168677176</v>
       </c>
       <c r="F21">
         <v>123456</v>
@@ -14434,7 +14434,7 @@
       </c>
       <c r="E22" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>40449.835630422145</v>
+        <v>41071.151717485896</v>
       </c>
       <c r="F22">
         <v>123456</v>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="E23" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>37927.711663391347</v>
+        <v>42593.136400242525</v>
       </c>
       <c r="F23">
         <v>123456</v>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="E24" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39093.476815349713</v>
+        <v>37310.875236316417</v>
       </c>
       <c r="F24">
         <v>123456</v>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="E25" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43584.285195570497</v>
+        <v>37054.203420125843</v>
       </c>
       <c r="F25">
         <v>123456</v>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="E26" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>36262.448322953351</v>
+        <v>35503.549210529527</v>
       </c>
       <c r="F26">
         <v>123456</v>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="E27" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42667.01330628604</v>
+        <v>37491.38882098216</v>
       </c>
       <c r="F27">
         <v>123456</v>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="E28" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41631.193269291252</v>
+        <v>37410.709038620938</v>
       </c>
       <c r="F28">
         <v>123456</v>
@@ -14609,7 +14609,7 @@
       </c>
       <c r="E29" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41716.862927754912</v>
+        <v>40635.092734814985</v>
       </c>
       <c r="F29">
         <v>123456</v>
@@ -14634,7 +14634,7 @@
       </c>
       <c r="E30" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>43967.366703320571</v>
+        <v>39459.906610501086</v>
       </c>
       <c r="F30">
         <v>123456</v>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="E31" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>38796.286344776192</v>
+        <v>40142.555496799228</v>
       </c>
       <c r="F31">
         <v>123456</v>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="E32" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>42704.409366010652</v>
+        <v>35386.787004493635</v>
       </c>
       <c r="F32">
         <v>123456</v>
@@ -16313,10 +16313,10 @@
         <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="E12" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="F12" t="s">
         <v>1081</v>
@@ -16333,10 +16333,10 @@
         <v>11</v>
       </c>
       <c r="D13" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="E13" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="F13" t="s">
         <v>1081</v>
@@ -17053,7 +17053,7 @@
         <v>47</v>
       </c>
       <c r="D49" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="E49" t="s">
         <v>1171</v>
@@ -17073,7 +17073,7 @@
         <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="E50" t="s">
         <v>1171</v>
